--- a/research/traditional_assets/database/data/indonesia/indonesia_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0143</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0611</v>
+        <v>-0.0462</v>
       </c>
       <c r="G2">
-        <v>0.108192682590932</v>
+        <v>0.1397726648351648</v>
       </c>
       <c r="H2">
-        <v>0.108192682590932</v>
+        <v>0.1397726648351648</v>
       </c>
       <c r="I2">
-        <v>0.1026926392353088</v>
+        <v>0.141967032967033</v>
       </c>
       <c r="J2">
-        <v>0.09374907363710593</v>
+        <v>0.1220472619459224</v>
       </c>
       <c r="K2">
-        <v>223.405</v>
+        <v>206.508</v>
       </c>
       <c r="L2">
-        <v>0.1139513294874345</v>
+        <v>0.1418324175824176</v>
       </c>
       <c r="M2">
-        <v>35.719</v>
+        <v>51.69</v>
       </c>
       <c r="N2">
-        <v>0.009198341573959622</v>
+        <v>0.01136738490770185</v>
       </c>
       <c r="O2">
-        <v>0.1598845146706654</v>
+        <v>0.2503050729269568</v>
       </c>
       <c r="P2">
-        <v>35.719</v>
+        <v>51.69</v>
       </c>
       <c r="Q2">
-        <v>0.009198341573959622</v>
+        <v>0.01136738490770185</v>
       </c>
       <c r="R2">
-        <v>0.1598845146706654</v>
+        <v>0.2503050729269568</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1444.891</v>
+        <v>1095.94</v>
       </c>
       <c r="V2">
-        <v>0.3720877111660487</v>
+        <v>0.2410131904768188</v>
       </c>
       <c r="W2">
-        <v>0.02941475493079818</v>
+        <v>0.03715935875298945</v>
       </c>
       <c r="X2">
-        <v>0.07384014453602819</v>
+        <v>0.1127397959071354</v>
       </c>
       <c r="Y2">
-        <v>-0.04442538960523001</v>
+        <v>-0.07558043715414597</v>
       </c>
       <c r="Z2">
-        <v>0.661303907418195</v>
+        <v>0.5238299452281107</v>
       </c>
       <c r="AA2">
-        <v>0.03579725471650229</v>
+        <v>0.05842993806508763</v>
       </c>
       <c r="AB2">
-        <v>0.07373668928000429</v>
+        <v>0.1126714643834131</v>
       </c>
       <c r="AC2">
-        <v>-0.03794704091395838</v>
+        <v>-0.05447183769476598</v>
       </c>
       <c r="AD2">
-        <v>77.35900000000001</v>
+        <v>238.864</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>77.35900000000001</v>
+        <v>238.864</v>
       </c>
       <c r="AG2">
-        <v>-1367.532</v>
+        <v>-857.076</v>
       </c>
       <c r="AH2">
-        <v>0.01953234379288379</v>
+        <v>0.04990802501585848</v>
       </c>
       <c r="AI2">
-        <v>0.01456696153093665</v>
+        <v>0.04513029487050623</v>
       </c>
       <c r="AJ2">
-        <v>-0.5436059130219092</v>
+        <v>-0.2322608548609485</v>
       </c>
       <c r="AK2">
-        <v>-0.3537616072481794</v>
+        <v>-0.204220143613361</v>
       </c>
       <c r="AL2">
-        <v>95.09999999999999</v>
+        <v>76.64</v>
       </c>
       <c r="AM2">
-        <v>95.09999999999999</v>
+        <v>76.64</v>
       </c>
       <c r="AN2">
-        <v>0.3668354814540833</v>
+        <v>1.10323167661988</v>
       </c>
       <c r="AO2">
-        <v>2.117055730809674</v>
+        <v>2.697077244258873</v>
       </c>
       <c r="AP2">
-        <v>-6.484820895097733</v>
+        <v>-3.958542905044963</v>
       </c>
       <c r="AQ2">
-        <v>2.117055730809674</v>
+        <v>2.697077244258873</v>
       </c>
     </row>
     <row r="3">
@@ -722,28 +722,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.529</v>
-      </c>
-      <c r="E3">
-        <v>0.0412</v>
+        <v>0.182</v>
       </c>
       <c r="G3">
-        <v>0.08232529805935079</v>
+        <v>0.1425019628369537</v>
       </c>
       <c r="H3">
-        <v>0.08232529805935079</v>
+        <v>0.1425019628369537</v>
       </c>
       <c r="I3">
-        <v>0.07893133756853191</v>
+        <v>0.1053389165140016</v>
       </c>
       <c r="J3">
-        <v>0.06350005226082157</v>
+        <v>0.05266945825700078</v>
       </c>
       <c r="K3">
-        <v>2.04</v>
+        <v>-0.498</v>
       </c>
       <c r="L3">
-        <v>0.001775302410582195</v>
+        <v>-0.0006516618686207799</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -761,79 +758,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>432.5</v>
+        <v>291.5</v>
       </c>
       <c r="V3">
-        <v>0.213992380386918</v>
+        <v>0.1161215790941322</v>
       </c>
       <c r="W3">
-        <v>0.004487461504619446</v>
+        <v>-0.001057774001699235</v>
       </c>
       <c r="X3">
-        <v>0.07514836151539321</v>
+        <v>0.1181557075410854</v>
       </c>
       <c r="Y3">
-        <v>-0.07066090001077377</v>
+        <v>-0.1192134815427846</v>
       </c>
       <c r="Z3">
-        <v>2.588937704179339</v>
+        <v>6.888408148548765</v>
       </c>
       <c r="AA3">
-        <v>0.1643976795153995</v>
+        <v>0.3628087254371732</v>
       </c>
       <c r="AB3">
-        <v>0.07351435276258486</v>
+        <v>0.1134604789135023</v>
       </c>
       <c r="AC3">
-        <v>0.0908833267528146</v>
+        <v>0.2493482465236709</v>
       </c>
       <c r="AD3">
-        <v>73.7</v>
+        <v>220.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>73.7</v>
+        <v>220.5</v>
       </c>
       <c r="AG3">
-        <v>-358.8</v>
+        <v>-71</v>
       </c>
       <c r="AH3">
-        <v>0.03518235631086501</v>
+        <v>0.08074556906401054</v>
       </c>
       <c r="AI3">
-        <v>0.1166508388730611</v>
+        <v>0.2779528551619816</v>
       </c>
       <c r="AJ3">
-        <v>-0.2158455152499549</v>
+        <v>-0.02910671094166359</v>
       </c>
       <c r="AK3">
-        <v>-1.800301053687908</v>
+        <v>-0.141490633718613</v>
       </c>
       <c r="AL3">
-        <v>95.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="AM3">
-        <v>95.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="AN3">
-        <v>0.7653167185877466</v>
+        <v>2.549132947976879</v>
       </c>
       <c r="AO3">
-        <v>0.9537329127234491</v>
+        <v>1.059210526315789</v>
       </c>
       <c r="AP3">
-        <v>-3.725856697819315</v>
+        <v>-0.8208092485549133</v>
       </c>
       <c r="AQ3">
-        <v>0.9537329127234491</v>
+        <v>1.059210526315789</v>
       </c>
     </row>
     <row r="4">
@@ -853,46 +850,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0143</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="E4">
-        <v>0.0611</v>
+        <v>-0.0104</v>
       </c>
       <c r="G4">
-        <v>0.1550916063059224</v>
+        <v>0.1634325140146615</v>
       </c>
       <c r="H4">
-        <v>0.1550916063059224</v>
+        <v>0.1634325140146615</v>
       </c>
       <c r="I4">
-        <v>0.1793779292714103</v>
+        <v>0.3208279430789133</v>
       </c>
       <c r="J4">
-        <v>0.1791619042383093</v>
+        <v>0.3207449896624638</v>
       </c>
       <c r="K4">
-        <v>79.7</v>
+        <v>102.7</v>
       </c>
       <c r="L4">
-        <v>0.3395824456753302</v>
+        <v>0.4428633031479086</v>
       </c>
       <c r="M4">
-        <v>0.019</v>
+        <v>23.5</v>
       </c>
       <c r="N4">
-        <v>9.80898296334538e-05</v>
+        <v>0.07248611967921037</v>
       </c>
       <c r="O4">
-        <v>0.0002383939774153074</v>
+        <v>0.2288218111002921</v>
       </c>
       <c r="P4">
-        <v>0.019</v>
+        <v>23.5</v>
       </c>
       <c r="Q4">
-        <v>9.80898296334538e-05</v>
+        <v>0.07248611967921037</v>
       </c>
       <c r="R4">
-        <v>0.0002383939774153074</v>
+        <v>0.2288218111002921</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -901,55 +898,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>506.3</v>
+        <v>385.9</v>
       </c>
       <c r="V4">
-        <v>2.61383582860093</v>
+        <v>1.190314620604565</v>
       </c>
       <c r="W4">
-        <v>0.07121794298990261</v>
+        <v>0.08097453283923363</v>
       </c>
       <c r="X4">
-        <v>0.07395879906550869</v>
+        <v>0.1127667465272695</v>
       </c>
       <c r="Y4">
-        <v>-0.002740856075606077</v>
+        <v>-0.03179221368803592</v>
       </c>
       <c r="Z4">
-        <v>0.3152874798495433</v>
+        <v>0.3039238814185736</v>
       </c>
       <c r="AA4">
-        <v>0.05648750527234174</v>
+        <v>0.09748206220377627</v>
       </c>
       <c r="AB4">
-        <v>0.07370602007248957</v>
+        <v>0.1126817943550806</v>
       </c>
       <c r="AC4">
-        <v>-0.01721851480014783</v>
+        <v>-0.0151997321513043</v>
       </c>
       <c r="AD4">
-        <v>1.02</v>
+        <v>0.642</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.02</v>
+        <v>0.642</v>
       </c>
       <c r="AG4">
-        <v>-505.28</v>
+        <v>-385.258</v>
       </c>
       <c r="AH4">
-        <v>0.005238290879211175</v>
+        <v>0.001976345423313488</v>
       </c>
       <c r="AI4">
-        <v>0.0004808326890803839</v>
+        <v>0.0003146994032475802</v>
       </c>
       <c r="AJ4">
-        <v>1.621670197060145</v>
+        <v>6.309705525893413</v>
       </c>
       <c r="AK4">
-        <v>-0.3128629986006365</v>
+        <v>-0.2329050347551782</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -958,10 +955,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.02417061611374408</v>
+        <v>0.008548601864181092</v>
       </c>
       <c r="AP4">
-        <v>-11.97345971563981</v>
+        <v>-5.129933422103861</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PT Panin Financial Tbk (IDX:PNLF)</t>
+          <t>PT Asuransi Jiwa Syariah Jasa Mitra Abadi Tbk (IDX:JMAS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,28 +978,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0482</v>
-      </c>
-      <c r="E5">
-        <v>0.08160000000000001</v>
+        <v>0.555</v>
       </c>
       <c r="G5">
-        <v>0.2236900044033465</v>
+        <v>0.05128205128205129</v>
       </c>
       <c r="H5">
-        <v>0.2236900044033465</v>
+        <v>0.05128205128205129</v>
       </c>
       <c r="I5">
-        <v>0.2113606340819023</v>
+        <v>0.1194871794871795</v>
       </c>
       <c r="J5">
-        <v>0.2023770803086825</v>
+        <v>0.1075384615384615</v>
       </c>
       <c r="K5">
-        <v>127.4</v>
+        <v>0.423</v>
       </c>
       <c r="L5">
-        <v>0.5609863496257156</v>
+        <v>0.1084615384615385</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1026,55 +1020,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>429.6</v>
+        <v>3.97</v>
       </c>
       <c r="V5">
-        <v>1.114396887159533</v>
+        <v>0.5907738095238095</v>
       </c>
       <c r="W5">
-        <v>0.07825552825552826</v>
+        <v>0.05274314214463841</v>
       </c>
       <c r="X5">
-        <v>0.07385890595151375</v>
+        <v>0.1126424534155211</v>
       </c>
       <c r="Y5">
-        <v>0.004396622304014511</v>
+        <v>-0.05989931127088267</v>
       </c>
       <c r="Z5">
-        <v>0.1773249004450691</v>
+        <v>0.8478260869565218</v>
       </c>
       <c r="AA5">
-        <v>0.03588649561810087</v>
+        <v>0.09117391304347829</v>
       </c>
       <c r="AB5">
-        <v>0.07373182524535518</v>
+        <v>0.1126424534155211</v>
       </c>
       <c r="AC5">
-        <v>-0.03784532962725431</v>
+        <v>-0.02146854037204279</v>
       </c>
       <c r="AD5">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-428.58</v>
+        <v>-3.97</v>
       </c>
       <c r="AH5">
-        <v>0.002638932008692953</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.0005151463116534177</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>9.948467966573808</v>
+        <v>-1.443636363636364</v>
       </c>
       <c r="AK5">
-        <v>-0.2764283226480567</v>
+        <v>-1.064343163538874</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1083,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>0.02035928143712575</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>-8.554491017964072</v>
+        <v>-7.518939393939394</v>
       </c>
     </row>
     <row r="6">
@@ -1097,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PT Bhakti Multi Artha Tbk (IDX:BHAT)</t>
+          <t>PT Panin Financial Tbk (IDX:PNLF)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1105,95 +1099,104 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>-0.106</v>
+      </c>
+      <c r="E6">
+        <v>-0.0462</v>
+      </c>
       <c r="G6">
-        <v>0.1092807424593968</v>
+        <v>0.2373949579831933</v>
       </c>
       <c r="H6">
-        <v>0.1092807424593968</v>
+        <v>0.2373949579831933</v>
       </c>
       <c r="I6">
-        <v>0.1415313225058005</v>
+        <v>0.1922268907563025</v>
       </c>
       <c r="J6">
-        <v>0.1415313225058005</v>
+        <v>0.1858193277310924</v>
       </c>
       <c r="K6">
-        <v>1.16</v>
+        <v>90.3</v>
       </c>
       <c r="L6">
-        <v>0.1345707656612529</v>
+        <v>0.4742647058823529</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>23.5</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.03202943982554177</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.2602436323366556</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>23.5</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.03202943982554177</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.2602436323366556</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>0.571</v>
+        <v>335.2</v>
       </c>
       <c r="V6">
-        <v>0.001631428571428571</v>
+        <v>0.456862477851983</v>
       </c>
       <c r="W6">
-        <v>0.0332378223495702</v>
+        <v>0.0492527544452929</v>
       </c>
       <c r="X6">
-        <v>0.07376771861440025</v>
+        <v>0.1126973748095907</v>
       </c>
       <c r="Y6">
-        <v>-0.04052989626483005</v>
+        <v>-0.06344462036429777</v>
       </c>
       <c r="Z6">
-        <v>0.2522976058069425</v>
+        <v>0.135533377941658</v>
       </c>
       <c r="AA6">
-        <v>0.03570801381490371</v>
+        <v>0.02518472117424296</v>
       </c>
       <c r="AB6">
-        <v>0.07375676601556616</v>
+        <v>0.1126598561917321</v>
       </c>
       <c r="AC6">
-        <v>-0.03804875220066245</v>
+        <v>-0.08747513501748917</v>
       </c>
       <c r="AD6">
-        <v>0.089</v>
+        <v>0.642</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.089</v>
+        <v>0.642</v>
       </c>
       <c r="AG6">
-        <v>-0.482</v>
+        <v>-334.558</v>
       </c>
       <c r="AH6">
-        <v>0.0002542210694994701</v>
+        <v>0.0008742520514964416</v>
       </c>
       <c r="AI6">
-        <v>0.002386762852315696</v>
+        <v>0.0003365764201480307</v>
       </c>
       <c r="AJ6">
-        <v>-0.001379041994975938</v>
+        <v>-0.8381929238215972</v>
       </c>
       <c r="AK6">
-        <v>-0.01312707663816112</v>
+        <v>-0.2127903974070149</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1202,10 +1205,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>0.06846153846153846</v>
+        <v>0.0168503937007874</v>
       </c>
       <c r="AP6">
-        <v>-0.3707692307692307</v>
+        <v>-8.781049868766404</v>
       </c>
     </row>
     <row r="7">
@@ -1216,7 +1219,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PT Asuransi Jiwa Sinarmas MSIG Tbk (IDX:LIFE)</t>
+          <t>PT Bhakti Multi Artha Tbk (IDX:BHAT)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1225,109 +1228,112 @@
         </is>
       </c>
       <c r="G7">
-        <v>0.08668639053254439</v>
+        <v>0.06752380952380951</v>
       </c>
       <c r="H7">
-        <v>0.08668639053254439</v>
+        <v>0.06752380952380951</v>
       </c>
       <c r="I7">
-        <v>0.0576923076923077</v>
+        <v>0.08933333333333333</v>
       </c>
       <c r="J7">
-        <v>0.04134615384615385</v>
+        <v>0.08933333333333333</v>
       </c>
       <c r="K7">
-        <v>13.3</v>
+        <v>0.283</v>
       </c>
       <c r="L7">
-        <v>0.0393491124260355</v>
+        <v>0.02695238095238095</v>
       </c>
       <c r="M7">
-        <v>35.7</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.03877484522645813</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>2.684210526315789</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>35.7</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.03877484522645813</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>2.684210526315789</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>72.5</v>
+        <v>1.27</v>
       </c>
       <c r="V7">
-        <v>0.07874443358314326</v>
+        <v>0.00458815028901734</v>
       </c>
       <c r="W7">
-        <v>0.02559168751202617</v>
+        <v>0.007648648648648648</v>
       </c>
       <c r="X7">
-        <v>0.07382138312054264</v>
+        <v>0.1163385776643363</v>
       </c>
       <c r="Y7">
-        <v>-0.04822969560851647</v>
+        <v>-0.1086899290156876</v>
       </c>
       <c r="Z7">
-        <v>0.7409729544871611</v>
+        <v>0.2875294375376526</v>
       </c>
       <c r="AA7">
-        <v>0.03063638177206532</v>
+        <v>0.02568596308669697</v>
       </c>
       <c r="AB7">
-        <v>0.0737415533146534</v>
+        <v>0.1137494688125424</v>
       </c>
       <c r="AC7">
-        <v>-0.04310517154258808</v>
+        <v>-0.08806350572584543</v>
       </c>
       <c r="AD7">
-        <v>1.53</v>
+        <v>16.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1.53</v>
+        <v>16.3</v>
       </c>
       <c r="AG7">
-        <v>-70.97</v>
+        <v>15.03</v>
       </c>
       <c r="AH7">
-        <v>0.001659022152825217</v>
+        <v>0.05561241896963493</v>
       </c>
       <c r="AI7">
-        <v>0.00287523725405446</v>
+        <v>0.3146718146718147</v>
       </c>
       <c r="AJ7">
-        <v>-0.08352064773516293</v>
+        <v>0.05150258712263989</v>
       </c>
       <c r="AK7">
-        <v>-0.1544068054739682</v>
+        <v>0.297447061151791</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AN7">
-        <v>0.07251184834123223</v>
+        <v>16.54822335025381</v>
+      </c>
+      <c r="AO7">
+        <v>1.465625</v>
       </c>
       <c r="AP7">
-        <v>-3.363507109004739</v>
+        <v>15.25888324873097</v>
+      </c>
+      <c r="AQ7">
+        <v>1.465625</v>
       </c>
     </row>
     <row r="8">
@@ -1338,7 +1344,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PT Asuransi Jiwa Syariah Jasa Mitra Abadi Tbk (IDX:JMAS)</t>
+          <t>PT Asuransi Jiwa Sinarmas MSIG Tbk (IDX:LIFE)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1346,95 +1352,104 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D8">
+        <v>-0.191</v>
+      </c>
+      <c r="E8">
+        <v>-0.212</v>
+      </c>
       <c r="G8">
-        <v>0.02425249169435216</v>
+        <v>0.04155233241865935</v>
       </c>
       <c r="H8">
-        <v>0.02425249169435216</v>
+        <v>0.04155233241865935</v>
       </c>
       <c r="I8">
-        <v>-0.06245847176079734</v>
+        <v>0.05409643277146218</v>
       </c>
       <c r="J8">
-        <v>-0.06245847176079734</v>
+        <v>0.04282901008770201</v>
       </c>
       <c r="K8">
-        <v>-0.195</v>
+        <v>13.3</v>
       </c>
       <c r="L8">
-        <v>-0.06478405315614619</v>
+        <v>0.05213641709133673</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>4.69</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.006743350107836089</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>0.3526315789473684</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>4.69</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.006743350107836089</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>0.3526315789473684</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>3.42</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="V8">
-        <v>0.280327868852459</v>
+        <v>0.112293314162473</v>
       </c>
       <c r="W8">
-        <v>-0.02562417871222076</v>
+        <v>0.02506596306068602</v>
       </c>
       <c r="X8">
-        <v>0.07375802328112364</v>
+        <v>0.1127128452870013</v>
       </c>
       <c r="Y8">
-        <v>-0.09938220199334441</v>
+        <v>-0.08764688222631528</v>
       </c>
       <c r="Z8">
-        <v>0.5605214152700185</v>
+        <v>0.5550116397972282</v>
       </c>
       <c r="AA8">
-        <v>-0.03500931098696462</v>
+        <v>0.02377059911966752</v>
       </c>
       <c r="AB8">
-        <v>0.07375802328112364</v>
+        <v>0.1126611344117457</v>
       </c>
       <c r="AC8">
-        <v>-0.1087673342680883</v>
+        <v>-0.0888905352920782</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AG8">
-        <v>-3.42</v>
+        <v>-77.31999999999999</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.001120238984316654</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>0.001583820662768031</v>
       </c>
       <c r="AJ8">
-        <v>-0.3895216400911162</v>
+        <v>-0.1250768384612896</v>
       </c>
       <c r="AK8">
-        <v>-0.7434782608695653</v>
+        <v>-0.1865920169892369</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1443,10 +1458,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>-0</v>
+        <v>0.05098039215686274</v>
       </c>
       <c r="AP8">
-        <v>28.98305084745763</v>
+        <v>-5.053594771241829</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/indonesia/indonesia_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.09710000000000001</v>
+        <v>-0.08055</v>
       </c>
       <c r="E2">
-        <v>-0.0462</v>
+        <v>0.0258</v>
       </c>
       <c r="G2">
-        <v>0.1397726648351648</v>
+        <v>0.2360653022160052</v>
       </c>
       <c r="H2">
-        <v>0.1397726648351648</v>
+        <v>0.2360653022160052</v>
       </c>
       <c r="I2">
-        <v>0.141967032967033</v>
+        <v>0.1694526246042848</v>
       </c>
       <c r="J2">
-        <v>0.1220472619459224</v>
+        <v>0.143828256954305</v>
       </c>
       <c r="K2">
-        <v>206.508</v>
+        <v>205.181</v>
       </c>
       <c r="L2">
-        <v>0.1418324175824176</v>
+        <v>0.3776430096444084</v>
       </c>
       <c r="M2">
-        <v>51.69</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="N2">
-        <v>0.01136738490770185</v>
+        <v>0.04711648343589775</v>
       </c>
       <c r="O2">
-        <v>0.2503050729269568</v>
+        <v>0.3757657872804986</v>
       </c>
       <c r="P2">
-        <v>51.69</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="Q2">
-        <v>0.01136738490770185</v>
+        <v>0.04711648343589775</v>
       </c>
       <c r="R2">
-        <v>0.2503050729269568</v>
+        <v>0.3757657872804986</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1095.94</v>
+        <v>595.29</v>
       </c>
       <c r="V2">
-        <v>0.2410131904768188</v>
+        <v>0.3637869186064276</v>
       </c>
       <c r="W2">
-        <v>0.03715935875298945</v>
+        <v>0.04351014723192881</v>
       </c>
       <c r="X2">
-        <v>0.1127397959071354</v>
+        <v>0.09630324285017119</v>
       </c>
       <c r="Y2">
-        <v>-0.07558043715414597</v>
+        <v>-0.05279309561824239</v>
       </c>
       <c r="Z2">
-        <v>0.5238299452281107</v>
+        <v>0.1952805171634222</v>
       </c>
       <c r="AA2">
-        <v>0.05842993806508763</v>
+        <v>0.03292444670935656</v>
       </c>
       <c r="AB2">
-        <v>0.1126714643834131</v>
+        <v>0.09628762656281108</v>
       </c>
       <c r="AC2">
-        <v>-0.05447183769476598</v>
+        <v>-0.06336304193304182</v>
       </c>
       <c r="AD2">
-        <v>238.864</v>
+        <v>0.883</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>238.864</v>
+        <v>0.883</v>
       </c>
       <c r="AG2">
-        <v>-857.076</v>
+        <v>-594.4069999999999</v>
       </c>
       <c r="AH2">
-        <v>0.04990802501585848</v>
+        <v>0.0005393179917825773</v>
       </c>
       <c r="AI2">
-        <v>0.04513029487050623</v>
+        <v>0.0001905414203168943</v>
       </c>
       <c r="AJ2">
-        <v>-0.2322608548609485</v>
+        <v>-0.5704684331401403</v>
       </c>
       <c r="AK2">
-        <v>-0.204220143613361</v>
+        <v>-0.1471715005646377</v>
       </c>
       <c r="AL2">
-        <v>76.64</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>76.64</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>1.10323167661988</v>
-      </c>
-      <c r="AO2">
-        <v>2.697077244258873</v>
+        <v>0.00926091014924434</v>
       </c>
       <c r="AP2">
-        <v>-3.958542905044963</v>
-      </c>
-      <c r="AQ2">
-        <v>2.697077244258873</v>
+        <v>-6.234144755472117</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PT Capital Financial Indonesia Tbk (IDX:CASA)</t>
+          <t>PT Asuransi Jiwa Sinarmas MSIG Tbk (IDX:LIFE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,115 +716,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.182</v>
+        <v>-0.0859</v>
+      </c>
+      <c r="E3">
+        <v>-0.0609</v>
       </c>
       <c r="G3">
-        <v>0.1425019628369537</v>
+        <v>0.1279664960446719</v>
       </c>
       <c r="H3">
-        <v>0.1425019628369537</v>
+        <v>0.1279664960446719</v>
       </c>
       <c r="I3">
-        <v>0.1053389165140016</v>
+        <v>0.1074918566775244</v>
       </c>
       <c r="J3">
-        <v>0.05266945825700078</v>
+        <v>0.08304370880993865</v>
       </c>
       <c r="K3">
-        <v>-0.498</v>
+        <v>16.6</v>
       </c>
       <c r="L3">
-        <v>-0.0006516618686207799</v>
+        <v>0.07724523033969288</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>24</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.02918287937743191</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.44578313253012</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>24</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.02918287937743191</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.44578313253012</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>291.5</v>
+        <v>56.6</v>
       </c>
       <c r="V3">
-        <v>0.1161215790941322</v>
+        <v>0.06882295719844359</v>
       </c>
       <c r="W3">
-        <v>-0.001057774001699235</v>
+        <v>0.03376042302216799</v>
       </c>
       <c r="X3">
-        <v>0.1181557075410854</v>
+        <v>0.09628689812265956</v>
       </c>
       <c r="Y3">
-        <v>-0.1192134815427846</v>
+        <v>-0.06252647510049156</v>
       </c>
       <c r="Z3">
-        <v>6.888408148548765</v>
+        <v>0.5186061103335103</v>
       </c>
       <c r="AA3">
-        <v>0.3628087254371732</v>
+        <v>0.04306697481359095</v>
       </c>
       <c r="AB3">
-        <v>0.1134604789135023</v>
+        <v>0.09628526571904956</v>
       </c>
       <c r="AC3">
-        <v>0.2493482465236709</v>
+        <v>-0.05321829090545862</v>
       </c>
       <c r="AD3">
-        <v>220.5</v>
+        <v>0.035</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>220.5</v>
+        <v>0.035</v>
       </c>
       <c r="AG3">
-        <v>-71</v>
+        <v>-56.565</v>
       </c>
       <c r="AH3">
-        <v>0.08074556906401054</v>
+        <v>4.255655462133786e-05</v>
       </c>
       <c r="AI3">
-        <v>0.2779528551619816</v>
+        <v>7.275977839450352e-05</v>
       </c>
       <c r="AJ3">
-        <v>-0.02910671094166359</v>
+        <v>-0.07386055743077818</v>
       </c>
       <c r="AK3">
-        <v>-0.141490633718613</v>
+        <v>-0.1332712900679727</v>
       </c>
       <c r="AL3">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>2.549132947976879</v>
-      </c>
-      <c r="AO3">
-        <v>1.059210526315789</v>
+        <v>0.001434426229508197</v>
       </c>
       <c r="AP3">
-        <v>-0.8208092485549133</v>
-      </c>
-      <c r="AQ3">
-        <v>1.059210526315789</v>
+        <v>-2.318237704918033</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PT Paninvest Tbk (IDX:PNIN)</t>
+          <t>PT Asuransi Jiwa Syariah Jasa Mitra Abadi Tbk (IDX:JMAS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,103 +844,100 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.09710000000000001</v>
+        <v>0.416</v>
       </c>
       <c r="E4">
-        <v>-0.0104</v>
+        <v>0.391</v>
       </c>
       <c r="G4">
-        <v>0.1634325140146615</v>
+        <v>0.0585972850678733</v>
       </c>
       <c r="H4">
-        <v>0.1634325140146615</v>
+        <v>0.0585972850678733</v>
       </c>
       <c r="I4">
-        <v>0.3208279430789133</v>
+        <v>0.03778280542986426</v>
       </c>
       <c r="J4">
-        <v>0.3207449896624638</v>
+        <v>0.02468070354692746</v>
       </c>
       <c r="K4">
-        <v>102.7</v>
+        <v>0.081</v>
       </c>
       <c r="L4">
-        <v>0.4428633031479086</v>
+        <v>0.01832579185520362</v>
       </c>
       <c r="M4">
-        <v>23.5</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.07248611967921037</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.2288218111002921</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>23.5</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.07248611967921037</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.2288218111002921</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>385.9</v>
+        <v>6.49</v>
       </c>
       <c r="V4">
-        <v>1.190314620604565</v>
+        <v>1.634760705289672</v>
       </c>
       <c r="W4">
-        <v>0.08097453283923363</v>
+        <v>0.01031847133757962</v>
       </c>
       <c r="X4">
-        <v>0.1127667465272695</v>
+        <v>0.09628498987822416</v>
       </c>
       <c r="Y4">
-        <v>-0.03179221368803592</v>
+        <v>-0.08596651854064455</v>
       </c>
       <c r="Z4">
-        <v>0.3039238814185736</v>
+        <v>1.478260869565218</v>
       </c>
       <c r="AA4">
-        <v>0.09748206220377627</v>
+        <v>0.03648451828676234</v>
       </c>
       <c r="AB4">
-        <v>0.1126817943550806</v>
+        <v>0.09628498987822416</v>
       </c>
       <c r="AC4">
-        <v>-0.0151997321513043</v>
+        <v>-0.05980047159146182</v>
       </c>
       <c r="AD4">
-        <v>0.642</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.642</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-385.258</v>
+        <v>-6.49</v>
       </c>
       <c r="AH4">
-        <v>0.001976345423313488</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.0003146994032475802</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>6.309705525893413</v>
+        <v>2.575396825396826</v>
       </c>
       <c r="AK4">
-        <v>-0.2329050347551782</v>
+        <v>-4.355704697986576</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -955,10 +946,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.008548601864181092</v>
+        <v>0</v>
       </c>
       <c r="AP4">
-        <v>-5.129933422103861</v>
+        <v>-26.2753036437247</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PT Asuransi Jiwa Syariah Jasa Mitra Abadi Tbk (IDX:JMAS)</t>
+          <t>PT Panin Financial Tbk (IDX:PNLF)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,97 +969,103 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.555</v>
+        <v>-0.07519999999999999</v>
+      </c>
+      <c r="E5">
+        <v>0.0457</v>
       </c>
       <c r="G5">
-        <v>0.05128205128205129</v>
+        <v>0.2300413956238912</v>
       </c>
       <c r="H5">
-        <v>0.05128205128205129</v>
+        <v>0.2300413956238912</v>
       </c>
       <c r="I5">
-        <v>0.1194871794871795</v>
+        <v>0.2584269662921349</v>
       </c>
       <c r="J5">
-        <v>0.1075384615384615</v>
+        <v>0.2506377050958017</v>
       </c>
       <c r="K5">
-        <v>0.423</v>
+        <v>118.9</v>
       </c>
       <c r="L5">
-        <v>0.1084615384615385</v>
+        <v>0.7031342400946187</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>12.6</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.02292993630573248</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.1059714045416316</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>12.6</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.02292993630573248</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.1059714045416316</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>3.97</v>
+        <v>239.7</v>
       </c>
       <c r="V5">
-        <v>0.5907738095238095</v>
+        <v>0.4362147406733394</v>
       </c>
       <c r="W5">
-        <v>0.05274314214463841</v>
+        <v>0.06687665223015918</v>
       </c>
       <c r="X5">
-        <v>0.1126424534155211</v>
+        <v>0.09631958757768282</v>
       </c>
       <c r="Y5">
-        <v>-0.05989931127088267</v>
+        <v>-0.02944293534752364</v>
       </c>
       <c r="Z5">
-        <v>0.8478260869565218</v>
+        <v>0.1171586498556822</v>
       </c>
       <c r="AA5">
-        <v>0.09117391304347829</v>
+        <v>0.02936437513195076</v>
       </c>
       <c r="AB5">
-        <v>0.1126424534155211</v>
+        <v>0.09628998740657259</v>
       </c>
       <c r="AC5">
-        <v>-0.02146854037204279</v>
+        <v>-0.06692561227462182</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>0.424</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>0.424</v>
       </c>
       <c r="AG5">
-        <v>-3.97</v>
+        <v>-239.276</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.0007710156312508638</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.0002103358229686719</v>
       </c>
       <c r="AJ5">
-        <v>-1.443636363636364</v>
+        <v>-0.7713007375315899</v>
       </c>
       <c r="AK5">
-        <v>-1.064343163538874</v>
+        <v>-0.1347180714859998</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1077,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>0.009359823399558499</v>
       </c>
       <c r="AP5">
-        <v>-7.518939393939394</v>
+        <v>-5.282030905077263</v>
       </c>
     </row>
     <row r="6">
@@ -1091,7 +1088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PT Panin Financial Tbk (IDX:PNLF)</t>
+          <t>PT Paninvest Tbk (IDX:PNIN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1100,46 +1097,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.106</v>
+        <v>-0.105</v>
       </c>
       <c r="E6">
-        <v>-0.0462</v>
+        <v>0.0059</v>
       </c>
       <c r="G6">
-        <v>0.2373949579831933</v>
+        <v>0.3976759199483538</v>
       </c>
       <c r="H6">
-        <v>0.2373949579831933</v>
+        <v>0.3976759199483538</v>
       </c>
       <c r="I6">
-        <v>0.1922268907563025</v>
+        <v>0.1620400258231117</v>
       </c>
       <c r="J6">
-        <v>0.1858193277310924</v>
+        <v>0.1619562842076993</v>
       </c>
       <c r="K6">
-        <v>90.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L6">
-        <v>0.4742647058823529</v>
+        <v>0.4493221433182698</v>
       </c>
       <c r="M6">
-        <v>23.5</v>
+        <v>40.5</v>
       </c>
       <c r="N6">
-        <v>0.03202943982554177</v>
+        <v>0.1554702495201536</v>
       </c>
       <c r="O6">
-        <v>0.2602436323366556</v>
+        <v>0.581896551724138</v>
       </c>
       <c r="P6">
-        <v>23.5</v>
+        <v>40.5</v>
       </c>
       <c r="Q6">
-        <v>0.03202943982554177</v>
+        <v>0.1554702495201536</v>
       </c>
       <c r="R6">
-        <v>0.2602436323366556</v>
+        <v>0.581896551724138</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1148,55 +1145,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>335.2</v>
+        <v>292.5</v>
       </c>
       <c r="V6">
-        <v>0.456862477851983</v>
+        <v>1.122840690978887</v>
       </c>
       <c r="W6">
-        <v>0.0492527544452929</v>
+        <v>0.05325987144168962</v>
       </c>
       <c r="X6">
-        <v>0.1126973748095907</v>
+        <v>0.0963579704381187</v>
       </c>
       <c r="Y6">
-        <v>-0.06344462036429777</v>
+        <v>-0.04309809899642907</v>
       </c>
       <c r="Z6">
-        <v>0.135533377941658</v>
+        <v>0.1680878353889459</v>
       </c>
       <c r="AA6">
-        <v>0.02518472117424296</v>
+        <v>0.02722288124010909</v>
       </c>
       <c r="AB6">
-        <v>0.1126598561917321</v>
+        <v>0.09629552268003419</v>
       </c>
       <c r="AC6">
-        <v>-0.08747513501748917</v>
+        <v>-0.0690726414399251</v>
       </c>
       <c r="AD6">
-        <v>0.642</v>
+        <v>0.424</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.642</v>
+        <v>0.424</v>
       </c>
       <c r="AG6">
-        <v>-334.558</v>
+        <v>-292.076</v>
       </c>
       <c r="AH6">
-        <v>0.0008742520514964416</v>
+        <v>0.001624994251199583</v>
       </c>
       <c r="AI6">
-        <v>0.0003365764201480307</v>
+        <v>0.0001991242290980611</v>
       </c>
       <c r="AJ6">
-        <v>-0.8381929238215972</v>
+        <v>9.249936660754997</v>
       </c>
       <c r="AK6">
-        <v>-0.2127903974070149</v>
+        <v>-0.1590114240667587</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1205,263 +1202,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>0.0168503937007874</v>
+        <v>0.01669291338582677</v>
       </c>
       <c r="AP6">
-        <v>-8.781049868766404</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PT Bhakti Multi Artha Tbk (IDX:BHAT)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="G7">
-        <v>0.06752380952380951</v>
-      </c>
-      <c r="H7">
-        <v>0.06752380952380951</v>
-      </c>
-      <c r="I7">
-        <v>0.08933333333333333</v>
-      </c>
-      <c r="J7">
-        <v>0.08933333333333333</v>
-      </c>
-      <c r="K7">
-        <v>0.283</v>
-      </c>
-      <c r="L7">
-        <v>0.02695238095238095</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>-0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>-0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>1.27</v>
-      </c>
-      <c r="V7">
-        <v>0.00458815028901734</v>
-      </c>
-      <c r="W7">
-        <v>0.007648648648648648</v>
-      </c>
-      <c r="X7">
-        <v>0.1163385776643363</v>
-      </c>
-      <c r="Y7">
-        <v>-0.1086899290156876</v>
-      </c>
-      <c r="Z7">
-        <v>0.2875294375376526</v>
-      </c>
-      <c r="AA7">
-        <v>0.02568596308669697</v>
-      </c>
-      <c r="AB7">
-        <v>0.1137494688125424</v>
-      </c>
-      <c r="AC7">
-        <v>-0.08806350572584543</v>
-      </c>
-      <c r="AD7">
-        <v>16.3</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>16.3</v>
-      </c>
-      <c r="AG7">
-        <v>15.03</v>
-      </c>
-      <c r="AH7">
-        <v>0.05561241896963493</v>
-      </c>
-      <c r="AI7">
-        <v>0.3146718146718147</v>
-      </c>
-      <c r="AJ7">
-        <v>0.05150258712263989</v>
-      </c>
-      <c r="AK7">
-        <v>0.297447061151791</v>
-      </c>
-      <c r="AL7">
-        <v>0.64</v>
-      </c>
-      <c r="AM7">
-        <v>0.64</v>
-      </c>
-      <c r="AN7">
-        <v>16.54822335025381</v>
-      </c>
-      <c r="AO7">
-        <v>1.465625</v>
-      </c>
-      <c r="AP7">
-        <v>15.25888324873097</v>
-      </c>
-      <c r="AQ7">
-        <v>1.465625</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PT Asuransi Jiwa Sinarmas MSIG Tbk (IDX:LIFE)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>-0.191</v>
-      </c>
-      <c r="E8">
-        <v>-0.212</v>
-      </c>
-      <c r="G8">
-        <v>0.04155233241865935</v>
-      </c>
-      <c r="H8">
-        <v>0.04155233241865935</v>
-      </c>
-      <c r="I8">
-        <v>0.05409643277146218</v>
-      </c>
-      <c r="J8">
-        <v>0.04282901008770201</v>
-      </c>
-      <c r="K8">
-        <v>13.3</v>
-      </c>
-      <c r="L8">
-        <v>0.05213641709133673</v>
-      </c>
-      <c r="M8">
-        <v>4.69</v>
-      </c>
-      <c r="N8">
-        <v>0.006743350107836089</v>
-      </c>
-      <c r="O8">
-        <v>0.3526315789473684</v>
-      </c>
-      <c r="P8">
-        <v>4.69</v>
-      </c>
-      <c r="Q8">
-        <v>0.006743350107836089</v>
-      </c>
-      <c r="R8">
-        <v>0.3526315789473684</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="V8">
-        <v>0.112293314162473</v>
-      </c>
-      <c r="W8">
-        <v>0.02506596306068602</v>
-      </c>
-      <c r="X8">
-        <v>0.1127128452870013</v>
-      </c>
-      <c r="Y8">
-        <v>-0.08764688222631528</v>
-      </c>
-      <c r="Z8">
-        <v>0.5550116397972282</v>
-      </c>
-      <c r="AA8">
-        <v>0.02377059911966752</v>
-      </c>
-      <c r="AB8">
-        <v>0.1126611344117457</v>
-      </c>
-      <c r="AC8">
-        <v>-0.0888905352920782</v>
-      </c>
-      <c r="AD8">
-        <v>0.78</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0.78</v>
-      </c>
-      <c r="AG8">
-        <v>-77.31999999999999</v>
-      </c>
-      <c r="AH8">
-        <v>0.001120238984316654</v>
-      </c>
-      <c r="AI8">
-        <v>0.001583820662768031</v>
-      </c>
-      <c r="AJ8">
-        <v>-0.1250768384612896</v>
-      </c>
-      <c r="AK8">
-        <v>-0.1865920169892369</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>0.05098039215686274</v>
-      </c>
-      <c r="AP8">
-        <v>-5.053594771241829</v>
+        <v>-11.49905511811024</v>
       </c>
     </row>
   </sheetData>
